--- a/course-info/stat-331-s26-schedule.xlsx
+++ b/course-info/stat-331-s26-schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat331/stat331-calpoly-s26/course-info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43071A38-D38E-8343-A7F0-DFC578BD9108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08587C06-C8BA-784F-8053-0DAB34F0AC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-280" yWindow="5140" windowWidth="30240" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>week</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>Advanced Graphics</t>
+  </si>
+  <si>
+    <t>slides/week-1/w1-intro-r.qmd</t>
+  </si>
+  <si>
+    <t>student-versions/handouts/w1.1-handout.qmd</t>
   </si>
 </sst>
 </file>
@@ -539,8 +545,12 @@
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="G2" s="3"/>
       <c r="H2" s="1"/>
     </row>
